--- a/모의고사/코코모의고사2회_정답.xlsx
+++ b/모의고사/코코모의고사2회_정답.xlsx
@@ -946,7 +946,7 @@
   <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12.625" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
